--- a/artfynd/A 47800-2024 artfynd.xlsx
+++ b/artfynd/A 47800-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>

--- a/artfynd/A 47800-2024 artfynd.xlsx
+++ b/artfynd/A 47800-2024 artfynd.xlsx
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1656872</v>
+        <v>344735</v>
       </c>
       <c r="B2" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5741</v>
+        <v>1206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Grå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon confluens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ca 1 km NNV Karlsnäsgården, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516719.9292867663</v>
+        <v>516720</v>
       </c>
       <c r="R2" t="n">
-        <v>6241628.590026082</v>
+        <v>6241629</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,31 +752,16 @@
           <t>2011-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gul fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -797,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>344735</v>
+        <v>1656872</v>
       </c>
       <c r="B3" t="n">
-        <v>90695</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,43 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1206</v>
+        <v>5741</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grå taggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon confluens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ca 1 km NNV Karlsnäsgården, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516719.9292867663</v>
+        <v>516720</v>
       </c>
       <c r="R3" t="n">
-        <v>6241628.590026082</v>
+        <v>6241629</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,26 +854,21 @@
           <t>2011-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gul fruktkropp</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
